--- a/daily/2026-04-06.xlsx
+++ b/daily/2026-04-06.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +75,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1194,7 +1206,7 @@
         <v>-4.5</v>
       </c>
       <c r="T9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>20</v>
@@ -1284,7 +1296,6 @@
       <c r="V10" t="n">
         <v>28</v>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
         <v>-6.4</v>
       </c>
@@ -2674,7 +2685,6 @@
       <c r="V27" t="n">
         <v>10</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>-1.7</v>
       </c>
@@ -2752,7 +2762,6 @@
       <c r="V28" t="n">
         <v>10</v>
       </c>
-      <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
         <v>-36.8</v>
       </c>
@@ -3240,7 +3249,6 @@
       <c r="V34" t="n">
         <v>10</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-21.9</v>
       </c>
@@ -3318,7 +3326,6 @@
       <c r="V35" t="n">
         <v>9</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>-17.8</v>
       </c>
@@ -3478,7 +3485,6 @@
       <c r="V37" t="n">
         <v>9</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
         <v>-25.8</v>
       </c>
@@ -3556,7 +3562,6 @@
       <c r="V38" t="n">
         <v>9</v>
       </c>
-      <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
         <v>-2</v>
       </c>
@@ -3716,7 +3721,6 @@
       <c r="V40" t="n">
         <v>9</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>-33.6</v>
       </c>
@@ -3786,7 +3790,7 @@
         <v>0.3</v>
       </c>
       <c r="T41" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>21</v>
@@ -3794,7 +3798,6 @@
       <c r="V41" t="n">
         <v>23</v>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
         <v>5.9</v>
       </c>
@@ -3954,7 +3957,6 @@
       <c r="V43" t="n">
         <v>23</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>30.1</v>
       </c>
@@ -4032,7 +4034,6 @@
       <c r="V44" t="n">
         <v>9</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
         <v>-4.6</v>
       </c>
@@ -4274,7 +4275,6 @@
       <c r="V47" t="n">
         <v>9</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
         <v>-13.1</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>40</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>-2.3</v>
@@ -8323,1183 +8323,2717 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Onyeka Okongwu</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Okongwu scored 12 pts vs 14.5 line (-2.5), UNDER hit by 2.5 pts. Okongwu played 37 min (+7.6 vs L10 avg of 29.1) — 26% more than expected. Shooting efficiency was cold: 30.8% FG (-15.7% vs L10 avg of 46.5%). 4/13 from the field. Signals that called it correctly: Volume, Trend, Context, Defense, Pace (7/10 aligned). Counter-signals that were wrong: HR L30, HR L10, H2H. Projection model targeted 13.9 pts — actual 12 was 1.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Okongwu in this role.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Anunoby scored 22 pts vs 15.5 line (+6.5), UNDER missed by 6.5 pts. Minutes were as expected: 37 played vs L10 avg 34.2. Shooting was in line with averages: 50.0% FG (7/14, L10 avg 49.0%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, FG Trend. Projection model targeted 13.9 pts — actual 22 was 8.1 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Anunoby's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Hart scored 2 pts vs 11.5 line (-9.5), OVER missed by 9.5 pts. Minutes were as expected: 31 played vs L10 avg 31.5. Shooting efficiency was cold: 33.3% FG (-24.5% vs L10 avg of 57.8%). 1/3 from the field. Counter-signals that proved correct: HR L30, Trend. Signals that were wrong: Volume, HR L10, Context. Projection model targeted 13.9 pts — actual 2 was 11.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Alexander-Walker scored 36 pts vs 19.5 line (+16.5), OVER hit by 16.5 pts. Alexander-Walker played 39 min (+6.2 vs L10 avg of 32.8) — 19% more than expected. Shooting efficiency was hot: 63.2% FG (+10.5% vs L10 avg of 52.7%). 12/19 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 22.5 pts — actual 36 was 13.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Alexander-Walker's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Brunson scored 30 pts vs 25.5 line (+4.5), UNDER missed by 4.5 pts. Brunson played 39 min (+3.4 vs L10 avg of 35.8) — 9% more than expected. Shooting was in line with averages: 42.3% FG (11/26, L10 avg 45.9%). Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 25.0 pts — actual 30 was 5.0 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Brunson's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>CJ McCollum</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>WIN — McCollum scored 17 pts vs 17.5 line (-0.5), UNDER hit by 0.5 pts. McCollum played 35 min (+5.4 vs L10 avg of 29.2) — 18% more than expected. Shooting efficiency was cold: 36.8% FG (-14.1% vs L10 avg of 50.9%). 7/19 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.0 pts — actual 17 was 8.0 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms McCollum's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Towns scored 21 pts vs 19.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 32 played vs L10 avg 29.2. Shooting efficiency was hot: 75.0% FG (+20.1% vs L10 avg of 54.9%). 9/12 from the field. Signals that called it correctly: HR L30, HR L10, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: Volume, Trend, FG Trend. Projection model targeted 23.5 pts — actual 21 was 2.5 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Towns's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Landry Shamet</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Shamet scored 1 pts vs 8.5 line (-7.5), UNDER hit by 7.5 pts. Shamet played 21 min (-3.3 vs L10 avg of 24.5) — 13% less than expected. Shooting efficiency was cold: 0.0% FG (-39.2% vs L10 avg of 39.2%). 0/2 from the field. Signals that called it correctly: Trend, H2H, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.7 pts — actual 1 was 6.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Shamet's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Jonathan Kuminga</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Kuminga scored 5 pts vs 9.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 22 played vs L10 avg 19.8. Shooting was in line with averages: 33.3% FG (2/6, L10 avg 38.2%). Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.6 pts — actual 5 was 0.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Kuminga in this role.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Dyson Daniels</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Daniels scored 11 pts vs 11.5 line (-0.5), OVER missed by 0.5 pts. Daniels played 38 min (+5.7 vs L10 avg of 32.2) — 18% more than expected. Shooting efficiency was cold: 36.4% FG (-20.0% vs L10 avg of 56.4%). 4/11 from the field. Counter-signals that proved correct: Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.1 pts — actual 11 was 1.1 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Zaccharie Risacher</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Risacher scored 3 pts vs 5.5 line (-2.5), OVER missed by 2.5 pts. Risacher played 7 min (-9.4 vs L10 avg of 16.8) — 56% less than expected. Shooting efficiency was cold: 25.0% FG (-35.7% vs L10 avg of 60.7%). 1/4 from the field. Counter-signals that proved correct: Trend, Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.0 pts — actual 3 was 5.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Risacher for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Jalen Johnson</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 21 pts vs 21.5 line (-0.5), UNDER hit by 0.5 pts. Johnson played 41 min (+5.2 vs L10 avg of 35.4) — 15% more than expected. Shooting efficiency was cold: 42.1% FG (-6.5% vs L10 avg of 48.6%). 8/19 from the field. Signals that called it correctly: Trend, Context, Defense, H2H, Pace (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 19.1 pts — actual 21 was 1.9 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Johnson in this role.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>NYK @ ATL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bridges scored 15 pts vs 12.5 line (+2.5), OVER hit by 2.5 pts. Minutes were as expected: 32 played vs L10 avg 31.5. Shooting efficiency was hot: 53.8% FG (+6.3% vs L10 avg of 47.5%). 7/13 from the field. Signals that called it correctly: Volume, Trend, Context, Defense, H2H (8/10 aligned). Counter-signals that were wrong: HR L30, HR L10. Projection model targeted 12.9 pts — actual 15 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E15" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Banchero scored 31 pts vs 22.5 line (+8.5), UNDER missed by 8.5 pts. Banchero played 38 min (+3.6 vs L10 avg of 34.1) — 11% more than expected. Shooting efficiency was hot: 62.5% FG (+22.8% vs L10 avg of 39.7%). 10/16 from the field. Counter-signals that proved correct: Volume, HR L30, H2H. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 20.4 pts — actual 31 was 10.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Silva scored 12 pts vs 8.5 line (+3.5), OVER hit by 3.5 pts. Silva played 33 min (+6.8 vs L10 avg of 26.4) — 26% more than expected. Shooting was in line with averages: 50.0% FG (5/10, L10 avg 45.6%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 13.2 pts — actual 12 was 1.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Silva in this role.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 12 pts vs 11.5 line (+0.5), UNDER missed by 0.5 pts. Jr. played 18 min (-11.3 vs L10 avg of 29.7) — 38% less than expected. Shooting efficiency was cold: 50.0% FG (-6.4% vs L10 avg of 56.4%). 2/4 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, Defense, H2H. Projection model targeted 11.1 pts — actual 12 was 0.9 pts close (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Jr. for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Suggs scored 12 pts vs 13.5 line (-1.5), UNDER hit by 1.5 pts. Suggs played 34 min (+3.4 vs L10 avg of 30.5) — 11% more than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 41.7%). Signals that called it correctly: Volume, HR L10, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L30, Trend, FG Trend. Projection model targeted 8.1 pts — actual 12 was 3.9 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Suggs's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Anthony Black</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Black scored 14 pts vs 8.5 line (+5.5), OVER hit by 5.5 pts. Black played 16 min (-13.3 vs L10 avg of 28.8) — 46% less than expected. Shooting was in line with averages: 36.4% FG (4/11, L10 avg 37.4%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 10.4 pts — actual 14 was 3.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Black's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Bane scored 25 pts vs 19.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 32 played vs L10 avg 32.8. Shooting efficiency was hot: 52.9% FG (+7.8% vs L10 avg of 45.1%). 9/17 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 21.8 pts — actual 25 was 3.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Bane's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Paul Reed</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Reed scored 9 pts vs 9.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 19 played vs L10 avg 18.2. Shooting efficiency was cold: 57.1% FG (-6.7% vs L10 avg of 63.8%). 4/7 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 6.9 pts — actual 9 was 2.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Reed's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Daniss Jenkins</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jenkins scored 18 pts vs 18.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 34 played vs L10 avg 35.8. Shooting efficiency was hot: 54.5% FG (+9.3% vs L10 avg of 45.2%). 6/11 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 2.2 pts — actual 18 was 15.8 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Jenkins's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Thompson scored 8 pts vs 10.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 31 played vs L10 avg 28.3. Shooting efficiency was hot: 80.0% FG (+25.1% vs L10 avg of 54.9%). 4/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, FG Trend, Min Trend. Projection model targeted 8.1 pts — actual 8 was 0.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Thompson in this role.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Kevin Huerter</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E24" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Huerter scored 17 pts vs 12.5 line (+4.5), UNDER missed by 4.5 pts. Huerter played 32 min (+6.9 vs L10 avg of 24.8) — 28% more than expected. Shooting was in line with averages: 50.0% FG (7/14, L10 avg 45.9%). Counter-signals that proved correct: Trend, Defense, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.6 pts — actual 17 was 8.4 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Huerter's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Jevon Carter</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Carter scored 0 pts vs 6.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 19 played vs L10 avg 20.8. Shooting efficiency was cold: 0.0% FG (-39.6% vs L10 avg of 39.6%). 0/3 from the field. Signals that called it correctly: Trend, Context, Defense, H2H, Pace (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.1 pts — actual 0 was 5.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Carter's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Jalen Duren</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>DET @ ORL</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Duren scored 18 pts vs 21.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 32 played vs L10 avg 31.3. Shooting efficiency was hot: 77.8% FG (+11.1% vs L10 avg of 66.7%). 7/9 from the field. Signals that called it correctly: Context, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.0 pts — actual 18 was 2.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Duren in this role.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Cedric Coward</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Coward scored 12 pts vs 12.5 line (-0.5), UNDER hit by 0.5 pts. Coward played 18 min (-7.9 vs L10 avg of 25.4) — 31% less than expected. Shooting efficiency was hot: 83.3% FG (+39.3% vs L10 avg of 44.0%). 5/6 from the field. Signals that called it correctly: Context, Defense, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.6 pts — actual 12 was 3.4 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Coward's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>GG Jackson</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jackson scored 11 pts vs 16.5 line (-5.5), UNDER hit by 5.5 pts. Jackson played 18 min (-8.4 vs L10 avg of 26.5) — 32% less than expected. Shooting efficiency was cold: 33.3% FG (-19.3% vs L10 avg of 52.6%). 3/9 from the field. Signals that called it correctly: HR L30, Context, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L10, Trend. Projection model targeted 5.4 pts — actual 11 was 5.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jackson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Keon Ellis</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E29" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Ellis scored 19 pts vs 13.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 27 played vs L10 avg 26.2. Shooting efficiency was hot: 63.6% FG (+9.5% vs L10 avg of 54.1%). 7/11 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.9 pts — actual 19 was 13.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Evan Mobley</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="4" t="n">
         <v>21.5</v>
       </c>
+      <c r="E30" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Mobley scored 24 pts vs 21.5 line (+2.5), UNDER missed by 2.5 pts. Mobley played 26 min (-5.4 vs L10 avg of 31.1) — 17% less than expected. Shooting efficiency was hot: 81.8% FG (+18.0% vs L10 avg of 63.8%). 9/11 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 21.5 pts — actual 24 was 2.5 pts off (wrong direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Mobley for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Dennis Schröder</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Schröder scored 22 pts vs 14.5 line (+7.5), UNDER missed by 7.5 pts. Schröder played 29 min (+10.4 vs L10 avg of 18.9) — 55% more than expected. Shooting efficiency was hot: 66.7% FG (+31.1% vs L10 avg of 35.6%). 8/12 from the field. Counter-signals that proved correct: Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.4 pts — actual 22 was 12.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Jarrett Allen</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Allen scored 13 pts vs 15.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 25 played vs L10 avg 26.7. Shooting was in line with averages: 71.4% FG (5/7, L10 avg 70.5%). Signals that called it correctly: Trend, H2H, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 14.8 pts — actual 13 was 1.8 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Allen in this role.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Sam Merrill</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Merrill scored 21 pts vs 14.5 line (+6.5), UNDER missed by 6.5 pts. Minutes were as expected: 28 played vs L10 avg 28.7. Shooting was in line with averages: 43.8% FG (7/16, L10 avg 40.6%). Counter-signals that proved correct: Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.6 pts — actual 21 was 8.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Olivier-Maxence Prosper</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>CLE @ MEM</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Prosper scored 24 pts vs 12.5 line (+11.5), UNDER missed by 11.5 pts. Prosper played 19 min (-4.4 vs L10 avg of 23.8) — 18% less than expected. Shooting efficiency was hot: 83.3% FG (+29.9% vs L10 avg of 53.4%). 10/12 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, FG Trend, Min Trend. Projection model targeted 10.9 pts — actual 24 was 13.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Prosper for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 5 pts vs 10.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 29 played vs L10 avg 29.0. Shooting efficiency was cold: 28.6% FG (-15.8% vs L10 avg of 44.4%). 2/7 from the field. Signals that called it correctly: Trend, Defense, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.1 pts — actual 5 was 4.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E36" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Castle scored 19 pts vs 17.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 31 played vs L10 avg 30.5. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 49.3%). Signals that called it correctly: HR L10, Trend, Defense, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 17.2 pts — actual 19 was 1.8 pts close (wrong direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Castle in this role.</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Edgecombe scored 14 pts vs 12.5 line (+1.5), UNDER missed by 1.5 pts. Edgecombe played 41 min (+7.3 vs L10 avg of 33.5) — 22% more than expected. Shooting efficiency was cold: 40.0% FG (-11.5% vs L10 avg of 51.5%). 6/15 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Min Trend. Projection model targeted 3.2 pts — actual 14 was 10.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Maxey scored 15 pts vs 24.5 line (-9.5), UNDER hit by 9.5 pts. Minutes were as expected: 40 played vs L10 avg 37.1. Shooting efficiency was cold: 37.5% FG (-7.9% vs L10 avg of 45.4%). 6/16 from the field. Signals that called it correctly: Trend, Defense (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 24.0 pts — actual 15 was 9.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Maxey's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E39" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Fox scored 13 pts vs 15.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 26 played vs L10 avg 27.7. Shooting was in line with averages: 50.0% FG (6/12, L10 avg 49.0%). Signals that called it correctly: HR L30, HR L10, Trend, Context, Pace (7/10 aligned). Counter-signals that were wrong: Volume, Defense, H2H. Projection model targeted 14.0 pts — actual 13 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Fox in this role.</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E40" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Barlow scored 6 pts vs 5.5 line (+0.5), UNDER missed by 0.5 pts. Barlow played 16 min (-6.1 vs L10 avg of 22.1) — 28% less than expected. Shooting efficiency was cold: 50.0% FG (-8.3% vs L10 avg of 58.3%). 2/4 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Min Trend. Projection model targeted 2.5 pts — actual 6 was 3.5 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Barlow for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Victor Wembanyama</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Wembanyama scored 17 pts vs 28.5 line (-11.5), UNDER hit by 11.5 pts. Wembanyama played 16 min (-14.3 vs L10 avg of 30.0) — 48% less than expected. Shooting efficiency was hot: 63.6% FG (+12.7% vs L10 avg of 50.9%). 7/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Pace (5/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 19.4 pts — actual 17 was 2.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Wembanyama's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Johnson scored 13 pts vs 12.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 25 played vs L10 avg 23.1. Shooting efficiency was cold: 28.6% FG (-22.0% vs L10 avg of 50.6%). 4/14 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 12.0 pts — actual 13 was 1.0 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E43" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Harper scored 17 pts vs 11.5 line (+5.5), OVER hit by 5.5 pts. Harper played 28 min (+4.4 vs L10 avg of 23.5) — 19% more than expected. Shooting was in line with averages: 63.6% FG (7/11, L10 avg 59.5%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: H2H, Pace, Min Trend. Projection model targeted 21.6 pts — actual 17 was 4.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Harper's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E44" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — George scored 16 pts vs 17.5 line (-1.5), OVER missed by 1.5 pts. George played 38 min (+4.9 vs L10 avg of 33.2) — 15% more than expected. Shooting efficiency was cold: 33.3% FG (-13.5% vs L10 avg of 46.8%). 5/15 from the field. Counter-signals that proved correct: HR L30, Defense, H2H. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 18.4 pts — actual 16 was 2.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E45" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Champagnie scored 7 pts vs 10.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 27 played vs L10 avg 27.0. Shooting was in line with averages: 50.0% FG (3/6, L10 avg 47.3%). Counter-signals that proved correct: HR L30, H2H, Pace. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 12.1 pts — actual 7 was 5.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Vassell scored 9 pts vs 12.5 line (-3.5), OVER missed by 3.5 pts. Minutes were as expected: 30 played vs L10 avg 30.0. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 42.7%). Counter-signals that proved correct: HR L30, HR L10, Trend, Pace. Signals that were wrong: Volume, Context, Defense. Projection model targeted 14.2 pts — actual 9 was 5.2 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Vassell's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Joel Embiid</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>PHI @ SAS</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>27.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Embiid scored 34 pts vs 27.5 line (+6.5), UNDER missed by 6.5 pts. Embiid played 39 min (+5.9 vs L10 avg of 33.2) — 18% more than expected. Shooting efficiency was cold: 42.1% FG (-7.8% vs L10 avg of 49.9%). 8/19 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, FG Trend. Projection model targeted 13.0 pts — actual 34 was 21.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Aaron Gordon</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E48" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Gordon scored 23 pts vs 15.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 31 played vs L10 avg 28.7. Shooting efficiency was hot: 57.1% FG (+12.6% vs L10 avg of 44.5%). 8/14 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, H2H. Projection model targeted 11.6 pts — actual 23 was 11.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E49" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>WIN — III scored 6 pts vs 7.5 line (-1.5), UNDER hit by 1.5 pts. III played 23 min (+5.2 vs L10 avg of 17.8) — 29% more than expected. Shooting efficiency was cold: 50.0% FG (-10.1% vs L10 avg of 60.1%). 2/4 from the field. Signals that called it correctly: HR L30, HR L10, Trend, Context, Defense (7/10 aligned). Counter-signals that were wrong: Volume, Pace, Min Trend. Projection model targeted 4.9 pts — actual 6 was 1.1 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for III in this role.</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E50" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Camara scored 30 pts vs 14.5 line (+15.5), OVER hit by 15.5 pts. Camara played 35 min (+3.2 vs L10 avg of 31.7) — 10% more than expected. Shooting efficiency was hot: 62.5% FG (+7.2% vs L10 avg of 55.3%). 10/16 from the field. Signals that called it correctly: HR L10, Trend, Defense, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 14.6 pts — actual 30 was 15.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Camara's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Tim Hardaway Jr.</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 3 pts vs 11.5 line (-8.5), OVER missed by 8.5 pts. Minutes were as expected: 23 played vs L10 avg 23.7. Shooting efficiency was cold: 14.3% FG (-25.4% vs L10 avg of 39.7%). 1/7 from the field. Counter-signals that proved correct: HR L10, Trend, Pace, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 15.4 pts — actual 3 was 12.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Clingan scored 18 pts vs 12.5 line (+5.5), OVER hit by 5.5 pts. Clingan played 30 min (+4.2 vs L10 avg of 25.8) — 16% more than expected. Shooting was in line with averages: 46.2% FG (6/13, L10 avg 50.0%). Signals that called it correctly: Volume, HR L30, Context, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 16.1 pts — actual 18 was 1.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Clingan in this role.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Bruce Brown</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Brown scored 6 pts vs 7.5 line (-1.5), OVER missed by 1.5 pts. Brown played 24 min (+3.5 vs L10 avg of 20.7) — 17% more than expected. Shooting efficiency was cold: 16.7% FG (-32.0% vs L10 avg of 48.7%). 1/6 from the field. Counter-signals that proved correct: HR L30, Pace, Min Trend. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 9.3 pts — actual 6 was 3.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Jamal Murray</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>24.5</v>
       </c>
+      <c r="E54" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Murray scored 20 pts vs 24.5 line (-4.5), OVER missed by 4.5 pts. Minutes were as expected: 38 played vs L10 avg 37.4. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 50.2%). Counter-signals that proved correct: HR L30, HR L10, Pace. Signals that were wrong: Volume, Trend, Context. Projection model targeted 26.0 pts — actual 20 was 6.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Christian Braun</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Braun scored 8 pts vs 11.5 line (-3.5), OVER missed by 3.5 pts. Braun played 40 min (+8.8 vs L10 avg of 31.1) — 28% more than expected. Shooting was in line with averages: 57.1% FG (4/7, L10 avg 58.0%). Counter-signals that proved correct: HR L30, Pace, Min Trend. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 13.8 pts — actual 8 was 5.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Henderson scored 18 pts vs 14.5 line (+3.5), UNDER missed by 3.5 pts. Henderson played 36 min (+11.6 vs L10 avg of 24.1) — 48% more than expected. Shooting was in line with averages: 42.9% FG (6/14, L10 avg 43.4%). Counter-signals that proved correct: Trend, Pace, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.6 pts — actual 18 was 5.4 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Henderson's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Cameron Johnson</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 17 pts vs 12.5 line (+4.5), OVER hit by 4.5 pts. Johnson played 37 min (+7.0 vs L10 avg of 29.7) — 24% more than expected. Shooting efficiency was hot: 66.7% FG (+14.8% vs L10 avg of 51.9%). 6/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Pace, Min Trend. Projection model targeted 13.3 pts — actual 17 was 3.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>27.5</v>
       </c>
+      <c r="E58" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Jokić scored 35 pts vs 27.5 line (+7.5), UNDER missed by 7.5 pts. Jokić played 43 min (+7.1 vs L10 avg of 36.1) — 20% more than expected. Shooting efficiency was cold: 48.4% FG (-8.3% vs L10 avg of 56.7%). 15/31 from the field. Counter-signals that proved correct: Trend, Defense, H2H, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 25.5 pts — actual 35 was 9.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Avdija scored 26 pts vs 25.5 line (+0.5), UNDER missed by 0.5 pts. Avdija played 40 min (+7.7 vs L10 avg of 31.8) — 24% more than expected. Shooting was in line with averages: 40.0% FG (6/15, L10 avg 43.5%). Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 23.1 pts — actual 26 was 2.9 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>POR @ DEN</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>17.5</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>LOSS — Holiday scored 19 pts vs 17.5 line (+1.5), UNDER missed by 1.5 pts. Holiday played 39 min (+9.0 vs L10 avg of 29.9) — 30% more than expected. Shooting efficiency was cold: 36.8% FG (-6.3% vs L10 avg of 43.1%). 7/19 from the field. Counter-signals that proved correct: HR L30, Trend, Pace, Min Trend. Signals that were wrong: Volume, HR L10, Context. Projection model targeted 17.1 pts — actual 19 was 1.9 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-07 07:38</t>
+        </is>
       </c>
     </row>
   </sheetData>
